--- a/FinRL/taiwan_stock_.xlsx
+++ b/FinRL/taiwan_stock_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Isaac_WORK\private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8593E5A-E2AC-46FB-9098-8849D8CE993A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09222B9C-E72B-4E5F-B8CA-E805EFC619C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CB0707DF-3E0B-4A32-9B95-35D7B926E757}"/>
   </bookViews>
@@ -24,44 +24,53 @@
   <si>
     <t>元大台灣50 
 0050</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>元大高股息
 0056</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>元大S&amp;P500 
 00646</t>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>元大美債20年
 00679B</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>元大台灣高息低波
 00713</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
     <t>元大AAA至A公司債
 00751B</t>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>國泰永續高股息
 00878</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>即時庫存</t>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>玉山金
 2884</t>
-  </si>
-  <si>
-    <t>即時庫存</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -220,6 +229,25 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="33">
@@ -519,7 +547,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -646,16 +674,22 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 輔色1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 輔色2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 輔色3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -675,6 +709,7 @@
     <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
     <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="42" xr:uid="{892FC553-202D-4244-8A1E-C0F0025D0EF1}"/>
     <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
@@ -1010,43 +1045,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF61596-49CC-406B-88F6-E78A6874A4F3}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="68" x14ac:dyDescent="0.4">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:9" ht="68">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
       <c r="B2">
-        <v>1036</v>
+        <v>1089</v>
       </c>
       <c r="C2">
-        <v>16429</v>
+        <v>16673</v>
       </c>
       <c r="D2">
         <v>32</v>
@@ -1055,13 +1090,13 @@
         <v>23000</v>
       </c>
       <c r="F2">
-        <v>4686</v>
+        <v>4780</v>
       </c>
       <c r="G2">
         <v>1000</v>
       </c>
       <c r="H2">
-        <v>13836</v>
+        <v>14236</v>
       </c>
       <c r="I2">
         <v>20</v>

--- a/FinRL/taiwan_stock_.xlsx
+++ b/FinRL/taiwan_stock_.xlsx
@@ -1,258 +1,209 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Isaac_WORK\private\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09222B9C-E72B-4E5F-B8CA-E805EFC619C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CB0707DF-3E0B-4A32-9B95-35D7B926E757}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="taiwan_stock_" sheetId="1" r:id="rId1"/>
+    <sheet name="taiwan_stock_" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="opt6_cons_2020_2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="opt6_aggr_2020_2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="opt_full_aggr_2020_2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="opt_full_cons_2020_2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="opt_full_no00631_00632_cons" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>元大台灣50 
-0050</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>元大高股息
-0056</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>元大S&amp;P500 
-00646</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>元大美債20年
-00679B</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>元大台灣高息低波
-00713</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>元大AAA至A公司債
-00751B</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>國泰永續高股息
-00878</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>即時庫存</t>
-    <phoneticPr fontId="21" type="noConversion"/>
-  </si>
-  <si>
-    <t>玉山金
-2884</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="3"/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FF006100"/>
       <sz val="12"/>
-      <color rgb="FF006100"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FF9C0006"/>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FF9C5700"/>
       <sz val="12"/>
-      <color rgb="FF9C5700"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FF3F3F76"/>
       <sz val="12"/>
-      <color rgb="FF3F3F76"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
       <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
       <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FFFA7D00"/>
       <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
       <sz val="12"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
+      <color theme="0"/>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="2"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="2"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
       <sz val="12"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -299,19 +250,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -322,19 +273,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -345,19 +296,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="6" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -368,19 +319,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -391,19 +342,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -414,19 +365,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.5999938962981048"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.3999755851924192"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -462,7 +413,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.3999755851924192"/>
       </bottom>
       <diagonal/>
     </border>
@@ -548,202 +499,262 @@
     </border>
   </borders>
   <cellStyleXfs count="43">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="42">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="20% - 輔色1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 輔色6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 輔色6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 輔色6" xfId="41" builtinId="52" customBuiltin="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="42" xr:uid="{892FC553-202D-4244-8A1E-C0F0025D0EF1}"/>
-    <cellStyle name="中等" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="合計" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="備註" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="說明文字" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="輔色1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="輔色2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="輔色3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="輔色4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="輔色5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="輔色6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="標題" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="標題 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="標題 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="標題 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="標題 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="輸入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="輸出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="檢查儲存格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="壞" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="警告文字" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="標題" xfId="1" builtinId="15"/>
+    <cellStyle name="標題 1" xfId="2" builtinId="16"/>
+    <cellStyle name="標題 2" xfId="3" builtinId="17"/>
+    <cellStyle name="標題 3" xfId="4" builtinId="18"/>
+    <cellStyle name="標題 4" xfId="5" builtinId="19"/>
+    <cellStyle name="好" xfId="6" builtinId="26"/>
+    <cellStyle name="壞" xfId="7" builtinId="27"/>
+    <cellStyle name="中等" xfId="8" builtinId="28"/>
+    <cellStyle name="輸入" xfId="9" builtinId="20"/>
+    <cellStyle name="輸出" xfId="10" builtinId="21"/>
+    <cellStyle name="計算方式" xfId="11" builtinId="22"/>
+    <cellStyle name="連結的儲存格" xfId="12" builtinId="24"/>
+    <cellStyle name="檢查儲存格" xfId="13" builtinId="23"/>
+    <cellStyle name="警告文字" xfId="14" builtinId="11"/>
+    <cellStyle name="備註" xfId="15" builtinId="10"/>
+    <cellStyle name="說明文字" xfId="16" builtinId="53"/>
+    <cellStyle name="合計" xfId="17" builtinId="25"/>
+    <cellStyle name="輔色1" xfId="18" builtinId="29"/>
+    <cellStyle name="20% - 輔色1" xfId="19" builtinId="30"/>
+    <cellStyle name="40% - 輔色1" xfId="20" builtinId="31"/>
+    <cellStyle name="60% - 輔色1" xfId="21" builtinId="32"/>
+    <cellStyle name="輔色2" xfId="22" builtinId="33"/>
+    <cellStyle name="20% - 輔色2" xfId="23" builtinId="34"/>
+    <cellStyle name="40% - 輔色2" xfId="24" builtinId="35"/>
+    <cellStyle name="60% - 輔色2" xfId="25" builtinId="36"/>
+    <cellStyle name="輔色3" xfId="26" builtinId="37"/>
+    <cellStyle name="20% - 輔色3" xfId="27" builtinId="38"/>
+    <cellStyle name="40% - 輔色3" xfId="28" builtinId="39"/>
+    <cellStyle name="60% - 輔色3" xfId="29" builtinId="40"/>
+    <cellStyle name="輔色4" xfId="30" builtinId="41"/>
+    <cellStyle name="20% - 輔色4" xfId="31" builtinId="42"/>
+    <cellStyle name="40% - 輔色4" xfId="32" builtinId="43"/>
+    <cellStyle name="60% - 輔色4" xfId="33" builtinId="44"/>
+    <cellStyle name="輔色5" xfId="34" builtinId="45"/>
+    <cellStyle name="20% - 輔色5" xfId="35" builtinId="46"/>
+    <cellStyle name="40% - 輔色5" xfId="36" builtinId="47"/>
+    <cellStyle name="60% - 輔色5" xfId="37" builtinId="48"/>
+    <cellStyle name="輔色6" xfId="38" builtinId="49"/>
+    <cellStyle name="20% - 輔色6" xfId="39" builtinId="50"/>
+    <cellStyle name="40% - 輔色6" xfId="40" builtinId="51"/>
+    <cellStyle name="60% - 輔色6" xfId="41" builtinId="52"/>
+    <cellStyle name="一般 2" xfId="42"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1043,67 +1054,3638 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF61596-49CC-406B-88F6-E78A6874A4F3}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="16.54296875" customWidth="1" style="3" min="5" max="5"/>
+    <col width="19.6328125" customWidth="1" style="3" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="68">
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+    <row r="1" ht="68" customHeight="1" s="3">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>元大台灣50 
+0050</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>元大高股息
+0056</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>元大S&amp;P500 
+00646</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>元大美債20年
+00679B</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波
+00713</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>元大AAA至A公司債
+00751B</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>國泰永續高股息
+00878</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>玉山金
+2884</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>元大台灣50正2
+00631L</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50反1
+00632R</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>即時庫存</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>16673</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>4780</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>14236</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>積極型目標股數</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>3687</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>6243</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>5449</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>7065</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>8060</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>積極型建議增減股數</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>3598</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>-10430</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>669</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>-7171</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>8060</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>保守型目標股數</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>2840</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>8347</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>6317</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>9226</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>4426</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>保守型建議增減股數</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>2751</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>-8326</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>1537</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>-5010</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>4426</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>全投組保守型目標股數</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>3303</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>10771</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>1694</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>9090</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>4659</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>5449</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>12221</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>1089</v>
-      </c>
-      <c r="C2">
-        <v>16673</v>
-      </c>
-      <c r="D2">
-        <v>32</v>
-      </c>
-      <c r="E2">
-        <v>23000</v>
-      </c>
-      <c r="F2">
-        <v>4780</v>
-      </c>
-      <c r="G2">
-        <v>1000</v>
-      </c>
-      <c r="H2">
-        <v>14236</v>
-      </c>
-      <c r="I2">
-        <v>20</v>
+      <c r="K7" s="0" t="n">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>全投組保守型建議增減股數</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>3214</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>-5902</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>1662</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>-8910</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>3449</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>全投組積極型目標股數</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>2384</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>11318</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>2272</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>6607</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>5547</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>4029</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>11878</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>407</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2763</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>全投組積極型建議增減股數</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>2295</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>-5355</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>2240</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>-11393</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>767</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>2029</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>-2358</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>387</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>2763</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>全投組無00631_00632保守型目標股數</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>2849</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>9890</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>2102</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>10282</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>4747</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>4412</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>15024</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>全投組無00631_00632保守型建議增減股數</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>2760</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>-6783</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>2070</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>-7718</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>2412</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>788</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>portfolio_mode</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>existing_holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>initial_capital</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1422798.693595886</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>requested_train_range</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>2020-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>requested_backtest_range</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 ~ 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>actual_common_train_start</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>actual_backtest_end</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>portfolio_market_value</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>1422798.693595886</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_score</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>1.16554941365222</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_turnover</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0.3626232562888309</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_beta_vs_0050</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0.6857214800065423</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>當前投組訓練期</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0.1635278608941766</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>1.285710463323145</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>-0.2152175457681087</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組訓練期</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.2317686888133703</v>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>1.450722923530073</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>-0.2457489996896415</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>當前投組回測期</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>0.2783623754501592</v>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>1.517888554557851</v>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>-0.2070110682597217</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組回測期</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>0.3992601564601865</v>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>1.923559733657101</v>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>-0.2319646351573087</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Latest Price</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Current Shares</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Current Weight</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>Target Weight</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>Target Shares</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>Delta Shares</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Target Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0.005973789572802412</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0.190615356629986</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>2840</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>2751</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>271220</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>0056.TW</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>45.15000152587891</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>16673</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>0.5290881829097257</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>0.264875916204016</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>8347</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>-8326</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>376867.0627365112</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>00713.TW</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>55.15000152587891</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>4780</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>0.1852806081986575</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>0.2448720996263319</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>6317</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>1537</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>348382.5596389771</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>00878.TW</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>00878</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>國泰永續高股息</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>27.95000076293945</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>14236</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0.2796574193188144</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>0.1812464297356932</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>9226</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>-5010</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>257866.7070388794</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>00632R.TW</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>00632R</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50反1</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>11.3100004196167</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>0.01931921927970691</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>2430</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>2430</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>27483.30101966858</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>00631L.TW</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>0.09907097852426608</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>4426</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>4426</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>140968.101688385</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>portfolio_mode</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>existing_holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>initial_capital</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1422798.693595886</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>requested_train_range</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>2020-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>requested_backtest_range</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 ~ 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>actual_common_train_start</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>actual_backtest_end</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>portfolio_market_value</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>1422798.693595886</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_score</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0.8939400753809822</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_turnover</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>0.4718348491748764</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_beta_vs_0050</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>0.8216792086675999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>當前投組訓練期</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0.1635278486743312</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>1.285710174391866</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>-0.2152176463315322</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組訓練期</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.2608217545750386</v>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>1.401495747428581</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>-0.279705337636234</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>當前投組回測期</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>0.2783624517898415</v>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>1.517888612166684</v>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>-0.207010996223328</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組回測期</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>0.4985612678987017</v>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>2.10519562315323</v>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>-0.2606723211723883</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Latest Price</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Current Shares</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Current Weight</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>Target Weight</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>Target Shares</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>Delta Shares</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>Target Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0.005973789572802412</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0.2474759078101718</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>3687</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>3598</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>352108.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>0056.TW</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>45.15000152587891</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>16673</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>0.5290881829097257</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>0.198119311556751</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>6243</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>-10430</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>281871.459526062</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>00713.TW</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>55.15000152587891</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>4780</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>0.1852806081986575</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>0.2112157229493492</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>5449</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>669</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>300512.3583145142</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>00878.TW</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>00878</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>國泰永續高股息</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>27.95000076293945</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>14236</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0.2796574193188144</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>0.1387914414969126</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>7065</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>-7171</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>197466.7553901672</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>00632R.TW</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>00632R</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50反1</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>11.3100004196167</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>0.02396918010225719</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>3017</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>3017</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>34122.27126598358</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>00631L.TW</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>0.1804284360845582</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>8060</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>8060</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>256711.003074646</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>aggressive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>requested_train_range</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>2020-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>requested_backtest_range</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 ~ 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>actual_common_train_start</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>actual_backtest_end</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>portfolio_market_value</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1967327.690704346</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_score</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0.8232219260402908</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_turnover</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0.3103332321686716</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_beta_vs_0050</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0.5080439151590785</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>當前投組訓練期</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0.09239348181324081</v>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0.9531255564996877</v>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>-0.2115545532021791</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組訓練期</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0.1620138234868167</v>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>1.352226310513228</v>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>-0.2127970885457328</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>當前投組回測期</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0.1980136184357377</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>1.385172668434594</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>-0.1631481315071608</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組回測期</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.2870731219209799</v>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>1.692515704426056</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>-0.192263290473254</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Latest Price</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Current Shares</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Current Weight</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>Target Weight</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Target Shares</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>Delta Shares</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Target Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0.004320327538803155</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0.1157275454812592</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>2384</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>2295</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>227672</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>0056.TW</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>45.15000152587891</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>16673</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0.3826439179389913</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>0.2597488644566998</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>11318</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>-5355</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>511007.7172698975</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>00646.TW</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>00646</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>元大S&amp;P500</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0.001195530368994061</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0.08488580182263675</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>2272</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>2240</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>166992</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>00679B.TWO</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>00679B</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>元大美債20年</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>26.57999992370605</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>0.2431928350764062</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>0.08925878556214577</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>6607</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>-11393</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>175614.0594959259</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>00713.TW</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>55.15000152587891</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>4780</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>0.1339975076543149</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>0.1555069937215268</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>5547</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>767</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>305917.0584640503</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>00751B.TWO</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>00751B</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>元大AAA至A公司債</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>31.54999923706055</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0.03207396448099093</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>0.06462073087859252</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>4029</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>127114.9469261169</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>00878.TW</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>00878</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>國泰永續高股息</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>27.95000076293945</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>14236</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>0.2022521274626855</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>0.168747998290566</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>11878</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>-2358</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>331990.1090621948</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>2884.TW</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>0.0003237894788139412</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>0.006593784119554419</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>407</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>387</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>12962.95015525818</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>00632R.TW</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>00632R</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50反1</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>11.3100004196167</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>0.01017893327866269</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>1773</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>1773</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>20052.63074398041</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>00631L.TW</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>0.04473056238835633</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>2763</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>2763</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>88001.55105400085</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>requested_train_range</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>2020-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>requested_backtest_range</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>2025-01-01 ~ 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>actual_common_train_start</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>actual_backtest_end</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>portfolio_market_value</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1967327.690704346</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_score</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0.9619084929074589</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_turnover</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0.2879373740426592</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>optimizer_beta_vs_0050</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0.4447251940538945</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>當前投組訓練期</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>0.09239348426207994</v>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0.9531259067495627</v>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>-0.2115545810054431</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組訓練期</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>0.1422042735135862</v>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>1.271770562578265</v>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>-0.2071876251080348</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>當前投組回測期</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>0.1980136063487128</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>1.385172976101798</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>-0.1631480727420705</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>最佳化投組回測期</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>0.252638502072994</v>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>1.670911115369519</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>-0.1713305952556218</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Latest Price</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Current Shares</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Current Weight</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>Target Weight</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Target Shares</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>Delta Shares</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>Target Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0.004320327538803155</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0.1603257815842125</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>3303</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>3214</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>315436.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>0056.TW</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>45.15000152587891</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>16673</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0.3826439179389913</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>0.2471956531211318</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>10771</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>-5902</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>486310.6664352417</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>00646.TW</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>00646</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>元大S&amp;P500</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>0.001195530368994061</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0.0632949891760259</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>1694</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>1662</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>124509</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>00679B.TWO</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>00679B</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>元大美債20年</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>26.57999992370605</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>0.2431928350764062</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>0.1228128622641945</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>9090</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>-8910</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>241612.199306488</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>00713.TW</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>55.15000152587891</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>4780</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>0.1339975076543149</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>0.1306151665636663</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>4659</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>-121</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>256943.8571090698</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>00751B.TWO</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>00751B</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>元大AAA至A公司債</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>31.54999923706055</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0.03207396448099093</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>0.0873826304885609</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>5449</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>3449</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>171915.9458427429</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>00878.TW</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>00878</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>國泰永續高股息</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>27.95000076293945</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>14236</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>0.2022521274626855</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>0.1736145934527824</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>12221</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>341576.9593238831</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>2884.TW</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>0.0003237894788139412</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>0.0002345281667776493</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>445.9000053405762</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>00632R.TW</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>00632R</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50反1</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>11.3100004196167</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>0.01447416502546502</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>2518</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>2518</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>28478.58105659485</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>00631L.TW</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>4.963015718301561e-05</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>95.55000114440918</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>conservative</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>requested_train_range</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2020-01-01 ~ 2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>requested_backtest_range</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-01-01 ~ 2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>actual_common_train_start</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2020-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>actual_backtest_end</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>portfolio_market_value</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1967327.690704346</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>optimizer_score</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8977578793418941</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>optimizer_turnover</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2611927518937612</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>optimizer_beta_vs_0050</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4386788173202636</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>當前投組訓練期</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.09239348257672342</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9531254127224015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.2115546067256241</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>最佳化投組訓練期</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1259928125058827</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1.211602423015786</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.2062622370225269</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>當前投組回測期</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.1980136618186885</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1.385172530403331</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.1631481663181684</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>最佳化投組回測期</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAGR</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.2547264326123324</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1.640538042476917</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MDD</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.1753583104748556</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Latest Price</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Current Shares</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Current Weight</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Target Weight</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Target Shares</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Delta Shares</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Target Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0050.TW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>89</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.004320327538803155</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1382916394291065</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2849</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2760</v>
+      </c>
+      <c r="J18" t="n">
+        <v>272079.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0056.TW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>45.15000152587891</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16673</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3826439179389913</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2269831726438761</v>
+      </c>
+      <c r="H19" t="n">
+        <v>9890</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-6783</v>
+      </c>
+      <c r="J19" t="n">
+        <v>446533.5150909424</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00646.TW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>00646</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>元大S&amp;P500</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.001195530368994061</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.07853739746108598</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2102</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2070</v>
+      </c>
+      <c r="J20" t="n">
+        <v>154497</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00679B.TWO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>00679B</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>元大美債20年</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>26.57999992370605</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2431928350764062</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1389214807321968</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10282</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-7718</v>
+      </c>
+      <c r="J21" t="n">
+        <v>273295.5592155457</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00713.TW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>55.15000152587891</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4780</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1339975076543149</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.1330606447924407</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4747</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-33</v>
+      </c>
+      <c r="J22" t="n">
+        <v>261797.0572433472</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00751B.TWO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>00751B</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>元大AAA至A公司債</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>31.54999923706055</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.03207396448099093</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.07075346860173105</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4412</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2412</v>
+      </c>
+      <c r="J23" t="n">
+        <v>139198.5966339111</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00878.TW</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>00878</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>國泰永續高股息</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>27.95000076293945</v>
+      </c>
+      <c r="E24" t="n">
+        <v>14236</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.2022521274626855</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2134521962533113</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15024</v>
+      </c>
+      <c r="I24" t="n">
+        <v>788</v>
+      </c>
+      <c r="J24" t="n">
+        <v>419920.8114624023</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2884.TW</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>玉山金</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0003237894788139412</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.625157071766884e-11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00632R.TW</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>00632R</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>元大台灣50反1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.3100004196167</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00631L.TW</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>00631L</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>元大台灣50正2</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>